--- a/fhir/CodeSystem-ehealth-unit-code.xlsx
+++ b/fhir/CodeSystem-ehealth-unit-code.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -145,6 +145,15 @@
   </si>
   <si>
     <t>Number of occurrences in 30 seconds</t>
+  </si>
+  <si>
+    <t>1/60sec</t>
+  </si>
+  <si>
+    <t>one per 60 seconds</t>
+  </si>
+  <si>
+    <t>Number of occurrences in 60 seconds</t>
   </si>
   <si>
     <t>percentpoint</t>
@@ -461,7 +470,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -506,6 +515,20 @@
         <v>46</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/fhir/CodeSystem-ehealth-unit-code.xlsx
+++ b/fhir/CodeSystem-ehealth-unit-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-unit-code.xlsx
+++ b/fhir/CodeSystem-ehealth-unit-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-unit-code.xlsx
+++ b/fhir/CodeSystem-ehealth-unit-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-unit-code.xlsx
+++ b/fhir/CodeSystem-ehealth-unit-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-unit-code.xlsx
+++ b/fhir/CodeSystem-ehealth-unit-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-unit-code.xlsx
+++ b/fhir/CodeSystem-ehealth-unit-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
